--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124896614</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>595899</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6928417</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,264 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125011148</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595968</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6928409</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125011151</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57995</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595936</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6928421</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125011148</v>
+        <v>125011151</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,48 +915,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595968</v>
+        <v>595936</v>
       </c>
       <c r="R4" t="n">
-        <v>6928409</v>
+        <v>6928421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125011151</v>
+        <v>125011148</v>
       </c>
       <c r="B5" t="n">
-        <v>57995</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,49 +1047,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595936</v>
+        <v>595968</v>
       </c>
       <c r="R5" t="n">
-        <v>6928421</v>
+        <v>6928409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fångar mygg i luften nyfiken på oss.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125011151</v>
+        <v>125011148</v>
       </c>
       <c r="B4" t="n">
-        <v>57995</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,49 +915,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595936</v>
+        <v>595968</v>
       </c>
       <c r="R4" t="n">
-        <v>6928421</v>
+        <v>6928409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fångar mygg i luften nyfiken på oss.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125011148</v>
+        <v>125011151</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,48 +1041,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595968</v>
+        <v>595936</v>
       </c>
       <c r="R5" t="n">
-        <v>6928409</v>
+        <v>6928421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>124896614</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125011148</v>
+        <v>125011151</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>58111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,48 +915,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595968</v>
+        <v>595936</v>
       </c>
       <c r="R4" t="n">
-        <v>6928409</v>
+        <v>6928421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125011151</v>
+        <v>125011148</v>
       </c>
       <c r="B5" t="n">
-        <v>57995</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,49 +1047,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595936</v>
+        <v>595968</v>
       </c>
       <c r="R5" t="n">
-        <v>6928421</v>
+        <v>6928409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fångar mygg i luften nyfiken på oss.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125011151</v>
+        <v>125011148</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,49 +915,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595936</v>
+        <v>595968</v>
       </c>
       <c r="R4" t="n">
-        <v>6928421</v>
+        <v>6928409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fångar mygg i luften nyfiken på oss.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125011148</v>
+        <v>125011151</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>58111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,48 +1041,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595968</v>
+        <v>595936</v>
       </c>
       <c r="R5" t="n">
-        <v>6928409</v>
+        <v>6928421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -792,11 +792,6 @@
       <c r="B3" t="n">
         <v>91166</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>NT</t>
@@ -899,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125011148</v>
+        <v>125011151</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,48 +905,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595968</v>
+        <v>595936</v>
       </c>
       <c r="R4" t="n">
-        <v>6928409</v>
+        <v>6928421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,27 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125011151</v>
+        <v>125011148</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,49 +1032,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595936</v>
+        <v>595968</v>
       </c>
       <c r="R5" t="n">
-        <v>6928421</v>
+        <v>6928409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fångar mygg i luften nyfiken på oss.</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1130,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105899200</v>
+        <v>105899084</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595783.6748514737</v>
+        <v>595794</v>
       </c>
       <c r="R2" t="n">
-        <v>6928415.674119527</v>
+        <v>6928408</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124896614</v>
+        <v>124896591</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595899</v>
+        <v>595901</v>
       </c>
       <c r="R3" t="n">
-        <v>6928417</v>
+        <v>6928407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125011151</v>
+        <v>124896614</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,49 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595936</v>
+        <v>595899</v>
       </c>
       <c r="R4" t="n">
-        <v>6928421</v>
+        <v>6928417</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,27 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fångar mygg i luften nyfiken på oss.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,74 +974,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125011148</v>
+        <v>105899200</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595968</v>
+        <v>595783</v>
       </c>
       <c r="R5" t="n">
-        <v>6928409</v>
+        <v>6928416</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,15 +1071,910 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124120714</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spillkråka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595866</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6928388</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124247642</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spillkråka fjäder, Näsvattnet, Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595933</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6928381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tappad blodfjäder av Spillkråka. Spillkråkan har även observerats och hörts inom området vid upprepade olika tillfällen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126626263</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spillkråka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595866</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6928388</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125011151</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595936</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928421</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fångar mygg i luften nyfiken på oss.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124199280</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Talltita, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596095</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928397</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125011148</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595968</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928409</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124193487</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595943</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6928393</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124185717</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Garnlav , Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595943</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928393</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21663-2022 artfynd.xlsx
+++ b/artfynd/A 21663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896591</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124896614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124247642</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126626263</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125011151</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125011148</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124193487</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124185717</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,8 +2035,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124199280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>